--- a/src/main/resources/espacios/0 Step/0 - Anyone.xlsx
+++ b/src/main/resources/espacios/0 Step/0 - Anyone.xlsx
@@ -5,15 +5,15 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId4"/>
-    <sheet name="Sheet4" sheetId="4" state="visible" r:id="rId5"/>
-    <sheet name="Sheet5" sheetId="5" state="visible" r:id="rId6"/>
-    <sheet name="Sheet6" sheetId="6" state="visible" r:id="rId7"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Sheet4" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Sheet5" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Sheet6" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2143" uniqueCount="1609">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2142" uniqueCount="1609">
   <si>
     <t xml:space="preserve">Anyone can join the meeting.</t>
   </si>
@@ -4953,15 +4953,121 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="ffffff"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="ffffff"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18a303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369a3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="a33e03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8e03a3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="c99c00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="c9211e"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000ee"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551a8b"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F90"/>
-  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="46.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="46.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="55.76"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="50.02"/>
@@ -6222,7 +6328,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="1" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
@@ -6231,12 +6337,12 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F90"/>
-  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="70.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="78.02"/>
@@ -7500,7 +7606,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
@@ -7509,12 +7615,12 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F90"/>
-  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="54.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="78.02"/>
@@ -8777,7 +8883,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
@@ -8786,12 +8892,12 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F120"/>
-  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="66.22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="69.9"/>
@@ -9630,9 +9736,6 @@
       <c r="D60" s="1" t="s">
         <v>978</v>
       </c>
-      <c r="F60" s="1" t="s">
-        <v>6</v>
-      </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
@@ -10474,7 +10577,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
@@ -10483,12 +10586,12 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F90"/>
-  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="54.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="71.18"/>
@@ -11751,7 +11854,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
@@ -11760,12 +11863,12 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F60"/>
-  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="58.99"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="64.34"/>
@@ -12611,7 +12714,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>

--- a/src/main/resources/espacios/0 Step/0 - Anyone.xlsx
+++ b/src/main/resources/espacios/0 Step/0 - Anyone.xlsx
@@ -4849,7 +4849,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -4870,6 +4870,13 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -4920,12 +4927,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5060,6 +5071,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="50.02"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1023" min="5" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="1024" style="2" width="11.54"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6344,6 +6356,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="76.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="19.45"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1023" min="6" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="1024" style="2" width="11.54"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7627,6 +7640,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="55.36"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1023" min="5" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="1024" style="2" width="11.54"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8910,6 +8924,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="76.1"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1023" min="5" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="1024" style="2" width="11.54"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10613,6 +10628,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="66.48"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1023" min="5" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="1024" style="2" width="11.54"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11896,6 +11912,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="63.06"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="5" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="1025" style="2" width="11.54"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
